--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-07T10:11:40+00:00</t>
+    <t>2026-01-26T07:03:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:03:23+00:00</t>
+    <t>2026-01-26T07:12:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:12:25+00:00</t>
+    <t>2026-01-26T07:23:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:23:42+00:00</t>
+    <t>2026-03-01T19:57:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:57:07+00:00</t>
+    <t>2026-03-10T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T09:54:59+00:00</t>
+    <t>2026-03-12T09:42:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T09:42:23+00:00</t>
+    <t>2026-03-15T19:53:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-15T19:53:47+00:00</t>
+    <t>2026-03-24T19:35:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T19:35:33+00:00</t>
+    <t>2026-03-24T20:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T20:07:54+00:00</t>
+    <t>2026-03-29T08:30:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1853" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1564" uniqueCount="338">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T08:30:46+00:00</t>
+    <t>2026-03-29T16:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -486,7 +486,7 @@
     <t>Funktionscode</t>
   </si>
   <si>
-    <t>Funktionscode der Abteilung laut LKF</t>
+    <t>Funktionscode inkl. Subcode der Abteilung laut LKF</t>
   </si>
   <si>
     <t>HealthcareService.identifier:Funktionscode.id</t>
@@ -682,42 +682,6 @@
   </si>
   <si>
     <t>Identifier.assigner</t>
-  </si>
-  <si>
-    <t>HealthcareService.identifier:Funktionssubcode</t>
-  </si>
-  <si>
-    <t>Funktionssubcode</t>
-  </si>
-  <si>
-    <t>Funktionssubcode der Abteilung laut LKF</t>
-  </si>
-  <si>
-    <t>HealthcareService.identifier:Funktionssubcode.id</t>
-  </si>
-  <si>
-    <t>HealthcareService.identifier:Funktionssubcode.extension</t>
-  </si>
-  <si>
-    <t>HealthcareService.identifier:Funktionssubcode.use</t>
-  </si>
-  <si>
-    <t>HealthcareService.identifier:Funktionssubcode.type</t>
-  </si>
-  <si>
-    <t>HealthcareService.identifier:Funktionssubcode.system</t>
-  </si>
-  <si>
-    <t>http://example.org/lkf-system/funktionssubcode</t>
-  </si>
-  <si>
-    <t>HealthcareService.identifier:Funktionssubcode.value</t>
-  </si>
-  <si>
-    <t>HealthcareService.identifier:Funktionssubcode.period</t>
-  </si>
-  <si>
-    <t>HealthcareService.identifier:Funktionssubcode.assigner</t>
   </si>
   <si>
     <t>HealthcareService.active</t>
@@ -1419,12 +1383,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ57"/>
+  <dimension ref="A1:AJ48"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="45.81640625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="43.00390625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="37.6796875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="15.1328125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.3203125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -3606,11 +3570,9 @@
         <v>214</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>215</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>20</v>
       </c>
@@ -3625,26 +3587,30 @@
         <v>20</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>144</v>
+        <v>215</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>216</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q22" s="2"/>
+      <c r="Q22" t="s" s="2">
+        <v>219</v>
+      </c>
       <c r="R22" t="s" s="2">
         <v>20</v>
       </c>
@@ -3688,13 +3654,13 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>143</v>
+        <v>214</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
@@ -3705,10 +3671,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>152</v>
+        <v>220</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3728,18 +3694,20 @@
         <v>20</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>82</v>
+        <v>221</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>153</v>
+        <v>222</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -3788,7 +3756,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>155</v>
+        <v>220</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>73</v>
@@ -3797,22 +3765,22 @@
         <v>80</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>156</v>
+        <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>20</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>158</v>
+        <v>225</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>137</v>
+        <v>20</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -3831,16 +3799,16 @@
         <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>125</v>
+        <v>226</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>159</v>
+        <v>227</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>140</v>
+        <v>229</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -3878,19 +3846,19 @@
         <v>20</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>128</v>
+        <v>20</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>161</v>
+        <v>20</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>129</v>
+        <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>162</v>
+        <v>225</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>73</v>
@@ -3902,51 +3870,49 @@
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>131</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>164</v>
+        <v>230</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>20</v>
+        <v>231</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>100</v>
+        <v>174</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>165</v>
+        <v>232</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>166</v>
+        <v>233</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>20</v>
       </c>
@@ -3955,7 +3921,7 @@
         <v>20</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>20</v>
+        <v>235</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>20</v>
@@ -3970,13 +3936,13 @@
         <v>20</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>104</v>
+        <v>236</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>169</v>
+        <v>237</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>170</v>
+        <v>238</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>20</v>
@@ -3994,13 +3960,13 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>171</v>
+        <v>230</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
@@ -4011,21 +3977,21 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>173</v>
+        <v>239</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>20</v>
+        <v>240</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -4040,17 +4006,13 @@
         <v>174</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>175</v>
+        <v>241</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>20</v>
       </c>
@@ -4059,7 +4021,7 @@
         <v>20</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>20</v>
+        <v>243</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>20</v>
@@ -4074,13 +4036,13 @@
         <v>20</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>179</v>
+        <v>236</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>180</v>
+        <v>244</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>181</v>
+        <v>245</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>20</v>
@@ -4098,13 +4060,13 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>182</v>
+        <v>239</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
@@ -4115,10 +4077,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>221</v>
+        <v>246</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>184</v>
+        <v>246</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4126,10 +4088,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -4141,32 +4103,28 @@
         <v>81</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>94</v>
+        <v>174</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>185</v>
+        <v>247</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>222</v>
+        <v>20</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>190</v>
+        <v>20</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>20</v>
@@ -4178,13 +4136,13 @@
         <v>20</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>20</v>
+        <v>249</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>20</v>
+        <v>251</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>20</v>
@@ -4202,13 +4160,13 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>191</v>
+        <v>246</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
@@ -4219,10 +4177,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>223</v>
+        <v>252</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>193</v>
+        <v>252</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4230,10 +4188,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -4245,17 +4203,15 @@
         <v>81</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>194</v>
+        <v>253</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>195</v>
+        <v>254</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -4268,7 +4224,7 @@
         <v>20</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>20</v>
@@ -4304,16 +4260,16 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>199</v>
+        <v>252</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>92</v>
@@ -4321,10 +4277,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>202</v>
+        <v>256</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4347,13 +4303,13 @@
         <v>81</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>204</v>
+        <v>257</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>205</v>
+        <v>258</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4404,7 +4360,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>206</v>
+        <v>256</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>73</v>
@@ -4421,10 +4377,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>225</v>
+        <v>259</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>208</v>
+        <v>259</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4447,16 +4403,16 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>209</v>
+        <v>260</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>210</v>
+        <v>261</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>211</v>
+        <v>262</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4506,7 +4462,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>73</v>
@@ -4523,10 +4479,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>226</v>
+        <v>264</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>226</v>
+        <v>264</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4543,30 +4499,26 @@
         <v>20</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>227</v>
+        <v>260</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q31" t="s" s="2">
-        <v>231</v>
-      </c>
+      <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
         <v>20</v>
       </c>
@@ -4610,7 +4562,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>226</v>
+        <v>264</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>73</v>
@@ -4627,10 +4579,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>232</v>
+        <v>267</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>232</v>
+        <v>267</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4653,17 +4605,15 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>233</v>
+        <v>268</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>234</v>
+        <v>269</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -4712,7 +4662,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>232</v>
+        <v>267</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>73</v>
@@ -4729,10 +4679,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>237</v>
+        <v>271</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>237</v>
+        <v>271</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4755,18 +4705,20 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>238</v>
+        <v>272</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>239</v>
+        <v>273</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>240</v>
+        <v>274</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>275</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>276</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
       </c>
@@ -4814,7 +4766,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>237</v>
+        <v>271</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>73</v>
@@ -4831,14 +4783,14 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>242</v>
+        <v>277</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>242</v>
+        <v>277</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>243</v>
+        <v>20</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -4854,19 +4806,19 @@
         <v>20</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>174</v>
+        <v>253</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>244</v>
+        <v>278</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>245</v>
+        <v>279</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>246</v>
+        <v>280</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -4877,7 +4829,7 @@
         <v>20</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>247</v>
+        <v>20</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>20</v>
@@ -4892,13 +4844,13 @@
         <v>20</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>248</v>
+        <v>20</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>249</v>
+        <v>20</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>250</v>
+        <v>20</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>20</v>
@@ -4916,7 +4868,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>242</v>
+        <v>277</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>73</v>
@@ -4933,14 +4885,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -4956,18 +4908,20 @@
         <v>20</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
         <v>174</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>253</v>
+        <v>282</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -4977,7 +4931,7 @@
         <v>20</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>255</v>
+        <v>20</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>20</v>
@@ -4992,13 +4946,13 @@
         <v>20</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>256</v>
+        <v>283</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>257</v>
+        <v>285</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>20</v>
@@ -5016,7 +4970,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>73</v>
@@ -5033,10 +4987,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>258</v>
+        <v>286</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>258</v>
+        <v>286</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5056,16 +5010,16 @@
         <v>20</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>174</v>
+        <v>287</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>259</v>
+        <v>288</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>260</v>
+        <v>289</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5092,13 +5046,13 @@
         <v>20</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>261</v>
+        <v>20</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>262</v>
+        <v>20</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>263</v>
+        <v>20</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>20</v>
@@ -5116,7 +5070,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>258</v>
+        <v>286</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>73</v>
@@ -5133,10 +5087,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5144,11 +5098,11 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G37" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="G37" t="s" s="2">
-        <v>74</v>
-      </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
       </c>
@@ -5156,16 +5110,16 @@
         <v>20</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>265</v>
+        <v>194</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>266</v>
+        <v>153</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>267</v>
+        <v>154</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5216,38 +5170,38 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>264</v>
+        <v>155</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>20</v>
+        <v>156</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>92</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>268</v>
+        <v>291</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>268</v>
+        <v>291</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
@@ -5256,18 +5210,20 @@
         <v>20</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>194</v>
+        <v>125</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>269</v>
+        <v>159</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -5316,61 +5272,63 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>268</v>
+        <v>162</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>92</v>
+        <v>131</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>20</v>
+        <v>293</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="J39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>272</v>
+        <v>125</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>273</v>
+        <v>294</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
       </c>
@@ -5418,27 +5376,27 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>271</v>
+        <v>296</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>92</v>
+        <v>131</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5461,13 +5419,13 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>272</v>
+        <v>174</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5494,10 +5452,10 @@
         <v>20</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>20</v>
+        <v>236</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="Z40" t="s" s="2">
         <v>20</v>
@@ -5518,7 +5476,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>73</v>
@@ -5535,10 +5493,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5558,18 +5516,20 @@
         <v>20</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -5618,7 +5578,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>73</v>
@@ -5635,10 +5595,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5661,20 +5621,18 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>284</v>
+        <v>174</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>20</v>
       </c>
@@ -5698,13 +5656,13 @@
         <v>20</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>20</v>
+        <v>236</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>20</v>
+        <v>309</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>20</v>
+        <v>310</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>20</v>
@@ -5722,7 +5680,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>73</v>
@@ -5739,10 +5697,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5765,16 +5723,16 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>265</v>
+        <v>174</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -5800,13 +5758,13 @@
         <v>20</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>20</v>
+        <v>236</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>20</v>
+        <v>315</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>20</v>
+        <v>316</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>20</v>
@@ -5824,7 +5782,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>73</v>
@@ -5841,10 +5799,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>293</v>
+        <v>317</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>293</v>
+        <v>317</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5870,13 +5828,13 @@
         <v>174</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>294</v>
+        <v>318</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>295</v>
+        <v>319</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -5902,13 +5860,13 @@
         <v>20</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>248</v>
+        <v>104</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>295</v>
+        <v>105</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>297</v>
+        <v>106</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>20</v>
@@ -5926,7 +5884,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>293</v>
+        <v>317</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>73</v>
@@ -5943,10 +5901,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>298</v>
+        <v>321</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>298</v>
+        <v>321</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5969,13 +5927,13 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>299</v>
+        <v>174</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6002,13 +5960,13 @@
         <v>20</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>20</v>
+        <v>236</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>20</v>
+        <v>324</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>20</v>
+        <v>325</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>20</v>
@@ -6026,7 +5984,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>298</v>
+        <v>321</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>73</v>
@@ -6043,10 +6001,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>302</v>
+        <v>326</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>302</v>
+        <v>326</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6069,13 +6027,13 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>153</v>
+        <v>327</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>154</v>
+        <v>328</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6126,7 +6084,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>155</v>
+        <v>326</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>73</v>
@@ -6135,22 +6093,22 @@
         <v>80</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>156</v>
+        <v>20</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>20</v>
+        <v>92</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>303</v>
+        <v>329</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>303</v>
+        <v>329</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>137</v>
+        <v>20</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6169,16 +6127,16 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>125</v>
+        <v>330</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>159</v>
+        <v>331</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>160</v>
+        <v>332</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>140</v>
+        <v>333</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6228,7 +6186,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>162</v>
+        <v>329</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>73</v>
@@ -6240,19 +6198,19 @@
         <v>20</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>131</v>
+        <v>92</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>304</v>
+        <v>334</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>304</v>
+        <v>334</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>305</v>
+        <v>20</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -6265,26 +6223,22 @@
         <v>20</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>125</v>
+        <v>335</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>306</v>
+        <v>336</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>20</v>
       </c>
@@ -6332,7 +6286,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>308</v>
+        <v>334</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>73</v>
@@ -6344,916 +6298,6 @@
         <v>20</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="C49" s="2"/>
-      <c r="D49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E49" s="2"/>
-      <c r="F49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K49" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
-      <c r="P49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q49" s="2"/>
-      <c r="R49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X49" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="AG49" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E50" s="2"/>
-      <c r="F50" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K50" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="O50" s="2"/>
-      <c r="P50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q50" s="2"/>
-      <c r="R50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="C51" s="2"/>
-      <c r="D51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K51" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="O51" s="2"/>
-      <c r="P51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q51" s="2"/>
-      <c r="R51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="C52" s="2"/>
-      <c r="D52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E52" s="2"/>
-      <c r="F52" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O52" s="2"/>
-      <c r="P52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q52" s="2"/>
-      <c r="R52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="C53" s="2"/>
-      <c r="D53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K53" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="O53" s="2"/>
-      <c r="P53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q53" s="2"/>
-      <c r="R53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="C54" s="2"/>
-      <c r="D54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E54" s="2"/>
-      <c r="F54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K54" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
-      <c r="P54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q54" s="2"/>
-      <c r="R54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="C55" s="2"/>
-      <c r="D55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E55" s="2"/>
-      <c r="F55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K55" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
-      <c r="P55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q55" s="2"/>
-      <c r="R55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="C56" s="2"/>
-      <c r="D56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E56" s="2"/>
-      <c r="F56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K56" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="O56" s="2"/>
-      <c r="P56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q56" s="2"/>
-      <c r="R56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="AG56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="C57" s="2"/>
-      <c r="D57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E57" s="2"/>
-      <c r="F57" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K57" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
-      <c r="P57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q57" s="2"/>
-      <c r="R57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
         <v>92</v>
       </c>
     </row>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T16:14:43+00:00</t>
+    <t>2026-04-07T06:39:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T06:39:12+00:00</t>
+    <t>2026-04-07T10:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T10:38:55+00:00</t>
+    <t>2026-04-07T11:10:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T11:10:24+00:00</t>
+    <t>2026-04-07T12:18:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T12:18:59+00:00</t>
+    <t>2026-04-07T19:20:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T19:20:35+00:00</t>
+    <t>2026-04-07T19:34:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T19:34:12+00:00</t>
+    <t>2026-04-08T06:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T06:34:39+00:00</t>
+    <t>2026-04-08T08:16:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T08:16:43+00:00</t>
+    <t>2026-04-17T10:34:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T10:34:11+00:00</t>
+    <t>2026-04-23T07:59:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T07:59:48+00:00</t>
+    <t>2026-04-29T07:12:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedKHOrganisationseinheit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T07:12:28+00:00</t>
+    <t>2026-04-29T07:28:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
